--- a/Team-Data/2012-13/2-13-2012-13.xlsx
+++ b/Team-Data/2012-13/2-13-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,91 +728,91 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
         <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.569</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J2" t="n">
-        <v>80.8</v>
+        <v>80.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L2" t="n">
         <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.381</v>
+        <v>0.384</v>
       </c>
       <c r="O2" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="P2" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Q2" t="n">
         <v>0.701</v>
       </c>
       <c r="R2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="S2" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T2" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="U2" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="V2" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W2" t="n">
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y2" t="n">
         <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA2" t="n">
         <v>19.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>97</v>
+        <v>96.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -754,10 +821,10 @@
         <v>8</v>
       </c>
       <c r="AI2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
@@ -781,7 +848,7 @@
         <v>27</v>
       </c>
       <c r="AR2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
         <v>12</v>
@@ -790,10 +857,10 @@
         <v>26</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -805,16 +872,16 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
         <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.538</v>
+        <v>0.529</v>
       </c>
       <c r="H3" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="I3" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="J3" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="L3" t="n">
         <v>5.6</v>
@@ -876,13 +943,13 @@
         <v>0.34</v>
       </c>
       <c r="O3" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R3" t="n">
         <v>8.6</v>
@@ -894,7 +961,7 @@
         <v>40</v>
       </c>
       <c r="U3" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="V3" t="n">
         <v>14.5</v>
@@ -915,13 +982,13 @@
         <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.8</v>
+        <v>96.3</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -930,16 +997,16 @@
         <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
         <v>8</v>
@@ -954,7 +1021,7 @@
         <v>27</v>
       </c>
       <c r="AO3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -1025,46 +1092,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>0.585</v>
+        <v>0.577</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J4" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.352</v>
+        <v>0.346</v>
       </c>
       <c r="O4" t="n">
         <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R4" t="n">
         <v>12.5</v>
@@ -1073,16 +1140,16 @@
         <v>29.8</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U4" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V4" t="n">
         <v>14.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X4" t="n">
         <v>4.8</v>
@@ -1091,28 +1158,28 @@
         <v>4.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA4" t="n">
         <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.2</v>
+        <v>94.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
         <v>9</v>
@@ -1124,19 +1191,19 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM4" t="n">
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
@@ -1148,16 +1215,16 @@
         <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1169,16 +1236,16 @@
         <v>6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" t="n">
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>0.231</v>
+        <v>0.235</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>34.3</v>
+        <v>34.5</v>
       </c>
       <c r="J5" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.421</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
@@ -1237,7 +1304,7 @@
         <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O5" t="n">
         <v>19.4</v>
@@ -1246,19 +1313,19 @@
         <v>25.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R5" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S5" t="n">
         <v>29.6</v>
       </c>
       <c r="T5" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U5" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="V5" t="n">
         <v>14.1</v>
@@ -1279,13 +1346,13 @@
         <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.9</v>
+        <v>-8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1357,7 +1424,7 @@
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -1389,67 +1456,67 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>0.577</v>
+        <v>0.588</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
         <v>4.8</v>
       </c>
       <c r="M6" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.344</v>
+        <v>0.348</v>
       </c>
       <c r="O6" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R6" t="n">
         <v>12.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T6" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U6" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
         <v>5.7</v>
@@ -1461,34 +1528,34 @@
         <v>20.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>1.6</v>
       </c>
       <c r="AD6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH6" t="n">
         <v>16</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK6" t="n">
         <v>23</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1497,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>7</v>
@@ -1518,10 +1585,10 @@
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>22</v>
@@ -1530,7 +1597,7 @@
         <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>0.302</v>
+        <v>0.308</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1589,40 +1656,40 @@
         <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>84.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="L7" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M7" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.761</v>
+        <v>0.759</v>
       </c>
       <c r="R7" t="n">
         <v>12.6</v>
       </c>
       <c r="S7" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T7" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U7" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V7" t="n">
         <v>14.4</v>
@@ -1637,25 +1704,25 @@
         <v>7.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB7" t="n">
         <v>97</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG7" t="n">
         <v>27</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1673,13 +1740,13 @@
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM7" t="n">
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AO7" t="n">
         <v>15</v>
@@ -1688,7 +1755,7 @@
         <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
         <v>8</v>
@@ -1703,13 +1770,13 @@
         <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>12</v>
       </c>
       <c r="AX7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY7" t="n">
         <v>29</v>
@@ -1721,7 +1788,7 @@
         <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -1753,112 +1820,112 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.442</v>
+        <v>0.431</v>
       </c>
       <c r="H8" t="n">
         <v>49</v>
       </c>
       <c r="I8" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J8" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="K8" t="n">
         <v>0.453</v>
       </c>
       <c r="L8" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="M8" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="N8" t="n">
         <v>0.367</v>
       </c>
       <c r="O8" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P8" t="n">
         <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S8" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V8" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AA8" t="n">
         <v>19.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.3</v>
+        <v>100.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
       </c>
       <c r="AF8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH8" t="n">
         <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
         <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN8" t="n">
         <v>8</v>
@@ -1867,22 +1934,22 @@
         <v>9</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
       </c>
       <c r="AR8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
         <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV8" t="n">
         <v>6</v>
@@ -1903,7 +1970,7 @@
         <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>19</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -1935,55 +2002,55 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
         <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>0.611</v>
+        <v>0.623</v>
       </c>
       <c r="H9" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I9" t="n">
         <v>40.3</v>
       </c>
       <c r="J9" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
       <c r="L9" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M9" t="n">
         <v>19.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.344</v>
+        <v>0.338</v>
       </c>
       <c r="O9" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="S9" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T9" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="U9" t="n">
         <v>23.9</v>
@@ -1992,25 +2059,25 @@
         <v>15.5</v>
       </c>
       <c r="W9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X9" t="n">
         <v>6.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA9" t="n">
         <v>22</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.1</v>
+        <v>105</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
         <v>3</v>
@@ -2037,16 +2104,16 @@
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
         <v>17</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
         <v>3</v>
@@ -2061,10 +2128,10 @@
         <v>10</v>
       </c>
       <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
         <v>2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3</v>
       </c>
       <c r="AV9" t="n">
         <v>28</v>
@@ -2073,13 +2140,13 @@
         <v>3</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY9" t="n">
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
         <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.389</v>
+        <v>0.377</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
@@ -2135,25 +2202,25 @@
         <v>36.4</v>
       </c>
       <c r="J10" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.446</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M10" t="n">
         <v>16.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.365</v>
+        <v>0.362</v>
       </c>
       <c r="O10" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P10" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q10" t="n">
         <v>0.697</v>
@@ -2162,37 +2229,37 @@
         <v>12.8</v>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U10" t="n">
         <v>20.6</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y10" t="n">
         <v>5.6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>5.5</v>
       </c>
       <c r="Z10" t="n">
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="AD10" t="n">
         <v>3</v>
@@ -2204,31 +2271,31 @@
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
         <v>13</v>
       </c>
       <c r="AI10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2249,10 +2316,10 @@
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX10" t="n">
         <v>8</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>-0.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>8</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2428,10 +2495,10 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW11" t="n">
         <v>28</v>
@@ -2446,10 +2513,10 @@
         <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
         <v>15</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>0.527</v>
+        <v>0.537</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2505,13 +2572,13 @@
         <v>0.462</v>
       </c>
       <c r="L12" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="M12" t="n">
         <v>28.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O12" t="n">
         <v>19.1</v>
@@ -2520,28 +2587,28 @@
         <v>25.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="R12" t="n">
         <v>10.9</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W12" t="n">
         <v>8.4</v>
       </c>
       <c r="X12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y12" t="n">
         <v>6.3</v>
@@ -2553,22 +2620,22 @@
         <v>19.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.1</v>
+        <v>106.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2577,7 +2644,7 @@
         <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK12" t="n">
         <v>6</v>
@@ -2589,19 +2656,19 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2610,13 +2677,13 @@
         <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="n">
         <v>27</v>
@@ -2631,10 +2698,10 @@
         <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2730,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" t="n">
         <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J13" t="n">
-        <v>81.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0.429</v>
@@ -2699,55 +2766,55 @@
         <v>16.5</v>
       </c>
       <c r="P13" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S13" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T13" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="U13" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W13" t="n">
         <v>6.8</v>
       </c>
       <c r="X13" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Y13" t="n">
         <v>5.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA13" t="n">
         <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>92.8</v>
+        <v>92.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE13" t="n">
         <v>8</v>
       </c>
-      <c r="AE13" t="n">
-        <v>7</v>
-      </c>
       <c r="AF13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG13" t="n">
         <v>8</v>
@@ -2759,7 +2826,7 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
@@ -2768,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN13" t="n">
         <v>19</v>
@@ -2789,34 +2856,34 @@
         <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="n">
         <v>26</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>28</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2863,46 +2930,46 @@
         <v>38.1</v>
       </c>
       <c r="J14" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L14" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O14" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P14" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q14" t="n">
         <v>0.702</v>
       </c>
       <c r="R14" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S14" t="n">
         <v>30.3</v>
       </c>
       <c r="T14" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W14" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="X14" t="n">
         <v>5.9</v>
@@ -2914,10 +2981,10 @@
         <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC14" t="n">
         <v>6.4</v>
@@ -2941,7 +3008,7 @@
         <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2953,10 +3020,10 @@
         <v>11</v>
       </c>
       <c r="AN14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -2968,16 +3035,16 @@
         <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -3105,22 +3172,22 @@
         <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH15" t="n">
         <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>19</v>
@@ -3129,13 +3196,13 @@
         <v>10</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3159,7 +3226,7 @@
         <v>16</v>
       </c>
       <c r="AV15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -3287,28 +3354,28 @@
         <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
         <v>11</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
@@ -3326,7 +3393,7 @@
         <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
@@ -3347,7 +3414,7 @@
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
         <v>21</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>6.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM17" t="n">
         <v>9</v>
@@ -3502,13 +3569,13 @@
         <v>3</v>
       </c>
       <c r="AO17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP17" t="n">
         <v>11</v>
       </c>
-      <c r="AP17" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
         <v>28</v>
@@ -3526,10 +3593,10 @@
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" t="n">
         <v>25</v>
       </c>
       <c r="G18" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
@@ -3591,7 +3658,7 @@
         <v>37.6</v>
       </c>
       <c r="J18" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0.432</v>
@@ -3600,10 +3667,10 @@
         <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O18" t="n">
         <v>15.8</v>
@@ -3612,19 +3679,19 @@
         <v>21.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R18" t="n">
         <v>13.1</v>
       </c>
       <c r="S18" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T18" t="n">
         <v>43.5</v>
       </c>
       <c r="U18" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V18" t="n">
         <v>14.4</v>
@@ -3639,7 +3706,7 @@
         <v>4.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA18" t="n">
         <v>19.7</v>
@@ -3648,10 +3715,10 @@
         <v>97.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3675,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM18" t="n">
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
@@ -3696,7 +3763,7 @@
         <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
@@ -3705,13 +3772,13 @@
         <v>15</v>
       </c>
       <c r="AV18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
         <v>6</v>
       </c>
       <c r="AX18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY18" t="n">
         <v>8</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -3755,67 +3822,67 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19" t="n">
         <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.38</v>
+        <v>0.388</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.5</v>
+        <v>35.7</v>
       </c>
       <c r="J19" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.439</v>
       </c>
       <c r="L19" t="n">
         <v>5.5</v>
       </c>
       <c r="M19" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.301</v>
+        <v>0.302</v>
       </c>
       <c r="O19" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="P19" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.732</v>
+        <v>0.73</v>
       </c>
       <c r="R19" t="n">
         <v>12.9</v>
       </c>
       <c r="S19" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T19" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U19" t="n">
         <v>21.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W19" t="n">
         <v>7.9</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="n">
         <v>6</v>
@@ -3827,7 +3894,7 @@
         <v>22.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC19" t="n">
         <v>-2.1</v>
@@ -3842,7 +3909,7 @@
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
         <v>27</v>
@@ -3851,7 +3918,7 @@
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3866,10 +3933,10 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
         <v>24</v>
@@ -3878,16 +3945,16 @@
         <v>5</v>
       </c>
       <c r="AS19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW19" t="n">
         <v>15</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
         <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>0.358</v>
+        <v>0.346</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J20" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="K20" t="n">
         <v>0.453</v>
@@ -3964,10 +4031,10 @@
         <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O20" t="n">
         <v>14.8</v>
@@ -3976,67 +4043,67 @@
         <v>19.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R20" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S20" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W20" t="n">
         <v>6.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3</v>
+        <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF20" t="n">
         <v>24</v>
       </c>
       <c r="AG20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI20" t="n">
         <v>24</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>23</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>15</v>
@@ -4054,7 +4121,7 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
         <v>17</v>
@@ -4066,10 +4133,10 @@
         <v>20</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4081,16 +4148,16 @@
         <v>23</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E21" t="n">
         <v>32</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>0.64</v>
+        <v>0.653</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J21" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.445</v>
+        <v>0.447</v>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="N21" t="n">
         <v>0.381</v>
       </c>
       <c r="O21" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="P21" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R21" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
         <v>29.9</v>
       </c>
       <c r="T21" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U21" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="V21" t="n">
         <v>11.6</v>
@@ -4179,22 +4246,22 @@
         <v>8</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z21" t="n">
         <v>18.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>100.3</v>
+        <v>100.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD21" t="n">
         <v>28</v>
@@ -4203,22 +4270,22 @@
         <v>7</v>
       </c>
       <c r="AF21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG21" t="n">
         <v>5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>6</v>
       </c>
       <c r="AH21" t="n">
         <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ21" t="n">
         <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4233,22 +4300,22 @@
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ21" t="n">
         <v>18</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4257,7 +4324,7 @@
         <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4266,7 +4333,7 @@
         <v>9</v>
       </c>
       <c r="BA21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
         <v>9</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
         <v>28</v>
@@ -4406,7 +4473,7 @@
         <v>9</v>
       </c>
       <c r="AM22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN22" t="n">
         <v>2</v>
@@ -4424,7 +4491,7 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT22" t="n">
         <v>11</v>
@@ -4439,7 +4506,7 @@
         <v>7</v>
       </c>
       <c r="AX22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY22" t="n">
         <v>4</v>
@@ -4451,7 +4518,7 @@
         <v>8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0.288</v>
+        <v>0.294</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
@@ -4504,70 +4571,70 @@
         <v>83.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L23" t="n">
         <v>6.6</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O23" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="P23" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.773</v>
+        <v>0.775</v>
       </c>
       <c r="R23" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S23" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T23" t="n">
         <v>42.8</v>
       </c>
       <c r="U23" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W23" t="n">
         <v>6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>94</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
       </c>
       <c r="AF23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG23" t="n">
         <v>29</v>
@@ -4588,10 +4655,10 @@
         <v>17</v>
       </c>
       <c r="AM23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4612,7 +4679,7 @@
         <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
         <v>13</v>
@@ -4621,7 +4688,7 @@
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY23" t="n">
         <v>14</v>
@@ -4633,10 +4700,10 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
         <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.431</v>
+        <v>0.44</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,7 +4750,7 @@
         <v>37.2</v>
       </c>
       <c r="J24" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.443</v>
@@ -4692,19 +4759,19 @@
         <v>6.1</v>
       </c>
       <c r="M24" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O24" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="P24" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.721</v>
+        <v>0.717</v>
       </c>
       <c r="R24" t="n">
         <v>10.9</v>
@@ -4716,25 +4783,25 @@
         <v>41.5</v>
       </c>
       <c r="U24" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W24" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X24" t="n">
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="AB24" t="n">
         <v>92.3</v>
@@ -4743,37 +4810,37 @@
         <v>-3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG24" t="n">
         <v>19</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>20</v>
       </c>
       <c r="AH24" t="n">
         <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,13 +4852,13 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
         <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU24" t="n">
         <v>13</v>
@@ -4806,10 +4873,10 @@
         <v>17</v>
       </c>
       <c r="AY24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
@@ -4818,7 +4885,7 @@
         <v>29</v>
       </c>
       <c r="BC24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>-5.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>26</v>
       </c>
       <c r="AF25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
         <v>26</v>
@@ -4940,10 +5007,10 @@
         <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
         <v>19</v>
@@ -4964,19 +5031,19 @@
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV25" t="n">
         <v>14</v>
@@ -4991,7 +5058,7 @@
         <v>18</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>28</v>
@@ -5000,7 +5067,7 @@
         <v>22</v>
       </c>
       <c r="BC25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -5029,88 +5096,88 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.472</v>
+        <v>0.481</v>
       </c>
       <c r="H26" t="n">
         <v>48.7</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="K26" t="n">
-        <v>0.442</v>
+        <v>0.444</v>
       </c>
       <c r="L26" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="O26" t="n">
         <v>16.3</v>
       </c>
       <c r="P26" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.779</v>
+        <v>0.776</v>
       </c>
       <c r="R26" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S26" t="n">
         <v>30.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U26" t="n">
         <v>21.2</v>
       </c>
       <c r="V26" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W26" t="n">
         <v>7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
         <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.7</v>
+        <v>97.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3</v>
+        <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF26" t="n">
         <v>17</v>
@@ -5122,67 +5189,67 @@
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AJ26" t="n">
         <v>15</v>
       </c>
       <c r="AK26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP26" t="n">
         <v>21</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>22</v>
       </c>
       <c r="AQ26" t="n">
         <v>8</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW26" t="n">
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5232,40 +5299,40 @@
         <v>83.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L27" t="n">
         <v>6.5</v>
       </c>
       <c r="M27" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O27" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="P27" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.757</v>
+        <v>0.754</v>
       </c>
       <c r="R27" t="n">
         <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="T27" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U27" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W27" t="n">
         <v>8.4</v>
@@ -5274,19 +5341,19 @@
         <v>4.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
         <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
         <v>96.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.9</v>
+        <v>-6.6</v>
       </c>
       <c r="AD27" t="n">
         <v>3</v>
@@ -5295,10 +5362,10 @@
         <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
         <v>20</v>
@@ -5307,10 +5374,10 @@
         <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>20</v>
@@ -5319,16 +5386,16 @@
         <v>20</v>
       </c>
       <c r="AN27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>17</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>16</v>
       </c>
       <c r="AR27" t="n">
         <v>11</v>
@@ -5343,7 +5410,7 @@
         <v>28</v>
       </c>
       <c r="AV27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
         <v>8</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F28" t="n">
         <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>0.778</v>
+        <v>0.774</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
@@ -5411,37 +5478,37 @@
         <v>39.6</v>
       </c>
       <c r="J28" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.487</v>
+        <v>0.488</v>
       </c>
       <c r="L28" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M28" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.384</v>
+        <v>0.386</v>
       </c>
       <c r="O28" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P28" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R28" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="S28" t="n">
         <v>33</v>
       </c>
       <c r="T28" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U28" t="n">
         <v>25</v>
@@ -5450,7 +5517,7 @@
         <v>14.6</v>
       </c>
       <c r="W28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X28" t="n">
         <v>5.1</v>
@@ -5462,13 +5529,13 @@
         <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.2</v>
+        <v>104.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AD28" t="n">
         <v>3</v>
@@ -5489,13 +5556,13 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
         <v>6</v>
@@ -5507,10 +5574,10 @@
         <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5525,16 +5592,16 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
         <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.396</v>
+        <v>0.385</v>
       </c>
       <c r="H29" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I29" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.444</v>
@@ -5605,34 +5672,34 @@
         <v>21.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O29" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P29" t="n">
         <v>22.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="R29" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S29" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U29" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="V29" t="n">
         <v>13</v>
       </c>
       <c r="W29" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X29" t="n">
         <v>4.6</v>
@@ -5641,19 +5708,19 @@
         <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
         <v>19.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5662,7 +5729,7 @@
         <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
         <v>3</v>
@@ -5677,25 +5744,25 @@
         <v>17</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AO29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS29" t="n">
         <v>28</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
         <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,19 +5842,19 @@
         <v>36.9</v>
       </c>
       <c r="J30" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.452</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M30" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O30" t="n">
         <v>18.4</v>
@@ -5802,13 +5869,13 @@
         <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T30" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U30" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V30" t="n">
         <v>14.9</v>
@@ -5838,7 +5905,7 @@
         <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
@@ -5850,49 +5917,49 @@
         <v>13</v>
       </c>
       <c r="AI30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
         <v>13</v>
       </c>
       <c r="AL30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV30" t="n">
         <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" t="n">
         <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>0.294</v>
+        <v>0.3</v>
       </c>
       <c r="H31" t="n">
         <v>48.7</v>
       </c>
       <c r="I31" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J31" t="n">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="L31" t="n">
         <v>6.5</v>
       </c>
       <c r="M31" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O31" t="n">
         <v>14.4</v>
@@ -5978,16 +6045,16 @@
         <v>19.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="R31" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T31" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="U31" t="n">
         <v>21.7</v>
@@ -6011,13 +6078,13 @@
         <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>91.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6041,7 +6108,7 @@
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
@@ -6062,16 +6129,16 @@
         <v>23</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
         <v>20</v>
       </c>
       <c r="AV31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
         <v>18</v>
@@ -6086,7 +6153,7 @@
         <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-13-2012-13</t>
+          <t>2013-02-13</t>
         </is>
       </c>
     </row>
